--- a/Unity/Assets/Config/Excel/StartConfig/RouterTest/StartSceneConfig@s.xlsx
+++ b/Unity/Assets/Config/Excel/StartConfig/RouterTest/StartSceneConfig@s.xlsx
@@ -1,282 +1,191 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="16507" windowHeight="9517" activeTab="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="16507" windowHeight="9517" tabRatio="600" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="StartSceneConfig" sheetId="1" r:id="rId1"/>
-    <sheet name="Router" sheetId="3" r:id="rId2"/>
+    <sheet name="StartSceneConfig" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Router" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="144525"/>
+  <definedNames/>
+  <calcPr calcId="144525" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="27">
-  <si>
-    <t>Id</t>
-  </si>
-  <si>
-    <t>所属进程</t>
-  </si>
-  <si>
-    <t>所属区</t>
-  </si>
-  <si>
-    <t>类型</t>
-  </si>
-  <si>
-    <t>名字</t>
-  </si>
-  <si>
-    <t>外网端口</t>
-  </si>
-  <si>
-    <t>Process</t>
-  </si>
-  <si>
-    <t>Zone</t>
-  </si>
-  <si>
-    <t>SceneType</t>
-  </si>
-  <si>
-    <t>Name</t>
-  </si>
-  <si>
-    <t>Port</t>
-  </si>
-  <si>
-    <t>int</t>
-  </si>
-  <si>
-    <t>string</t>
-  </si>
-  <si>
-    <t>Realm</t>
-  </si>
-  <si>
-    <t>Gate</t>
-  </si>
-  <si>
-    <t>Gate1</t>
-  </si>
-  <si>
-    <t>Gate2</t>
-  </si>
-  <si>
-    <t>Location</t>
-  </si>
-  <si>
-    <t>Map</t>
-  </si>
-  <si>
-    <t>Map1</t>
-  </si>
-  <si>
-    <t>Map2</t>
-  </si>
-  <si>
-    <t>RouterManager</t>
-  </si>
-  <si>
-    <t>Router</t>
-  </si>
-  <si>
-    <t>Router01</t>
-  </si>
-  <si>
-    <t>Router02</t>
-  </si>
-  <si>
-    <t>Router03</t>
-  </si>
-  <si>
-    <t>Router04</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9">
-  <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-  </numFmts>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
   <fonts count="22">
     <font>
-      <sz val="11"/>
+      <name val="宋体"/>
+      <charset val="134"/>
       <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="微软雅黑"/>
       <charset val="134"/>
-    </font>
-    <font>
-      <b/>
+      <color theme="1"/>
       <sz val="9"/>
-      <color theme="1"/>
+    </font>
+    <font>
       <name val="微软雅黑"/>
       <charset val="134"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
+      <b val="1"/>
+      <color theme="1"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
       <color rgb="FF0000FF"/>
+      <sz val="11"/>
+      <u val="single"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="宋体"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
       <color rgb="FF800080"/>
+      <sz val="11"/>
+      <u val="single"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="宋体"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color rgb="FFFF0000"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="18"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="宋体"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
+      <i val="1"/>
+      <color rgb="FF7F7F7F"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <b val="1"/>
       <color theme="3"/>
+      <sz val="15"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="宋体"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="13"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="宋体"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color rgb="FF3F3F76"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="宋体"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
+      <b val="1"/>
       <color rgb="FF3F3F3F"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="宋体"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
+      <b val="1"/>
       <color rgb="FFFA7D00"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="宋体"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
+      <b val="1"/>
       <color rgb="FFFFFFFF"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="宋体"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color rgb="FFFA7D00"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="宋体"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
+      <b val="1"/>
       <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="宋体"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color rgb="FF006100"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="宋体"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color rgb="FF9C0006"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="宋体"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color rgb="FF9C6500"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="宋体"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color theme="0"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="宋体"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="34">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -583,164 +492,164 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="5" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="4" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="6" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="6">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -796,11 +705,74 @@
     <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleMedium9"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -1089,377 +1061,457 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="C3:H11"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.35" outlineLevelCol="7"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="C1:H9"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="12.35"/>
   <cols>
-    <col min="1" max="1" width="21.1238938053097" style="2" customWidth="1"/>
-    <col min="2" max="2" width="12.7522123893805" style="2" customWidth="1"/>
-    <col min="3" max="5" width="12.6283185840708" style="3" customWidth="1"/>
-    <col min="6" max="6" width="15.3716814159292" style="3" customWidth="1"/>
-    <col min="7" max="8" width="13.1238938053097" style="3" customWidth="1"/>
-    <col min="9" max="16384" width="9" style="2"/>
+    <col width="21.1238938053097" customWidth="1" style="2" min="1" max="1"/>
+    <col width="12.7522123893805" customWidth="1" style="2" min="2" max="2"/>
+    <col width="12.6283185840708" customWidth="1" style="3" min="3" max="5"/>
+    <col width="15.3716814159292" customWidth="1" style="3" min="6" max="6"/>
+    <col width="13.1238938053097" customWidth="1" style="3" min="7" max="8"/>
+    <col width="9" customWidth="1" style="2" min="9" max="16384"/>
   </cols>
   <sheetData>
-    <row r="3" spans="3:8">
-      <c r="C3" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="D3" s="4" t="s">
+    <row r="1"/>
+    <row r="2"/>
+    <row r="3">
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>Id</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>所属进程</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>所属区</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>类型</t>
+        </is>
+      </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>名字</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>外网端口</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>Id</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>Process</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>Zone</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>SceneType</t>
+        </is>
+      </c>
+      <c r="G4" s="4" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>Port</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="G5" s="4" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" customFormat="1" s="1">
+      <c r="C6" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="E3" s="4" t="s">
+      <c r="D6" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F6" s="5" t="inlineStr">
+        <is>
+          <t>Realm</t>
+        </is>
+      </c>
+      <c r="G6" s="5" t="inlineStr">
+        <is>
+          <t>Realm</t>
+        </is>
+      </c>
+      <c r="H6" s="5" t="n">
+        <v>30002</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="C7" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="F3" s="4" t="s">
+      <c r="D7" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>Gate</t>
+        </is>
+      </c>
+      <c r="G7" s="3" t="inlineStr">
+        <is>
+          <t>Gate1</t>
+        </is>
+      </c>
+      <c r="H7" s="5" t="n">
+        <v>30003</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="C8" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="G3" s="4" t="s">
+      <c r="D8" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>Gate</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="inlineStr">
+        <is>
+          <t>Gate2</t>
+        </is>
+      </c>
+      <c r="H8" s="5" t="n">
+        <v>30004</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="C9" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="H3" s="4" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4" spans="3:8">
-      <c r="C4" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="E4" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="F4" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="G4" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="H4" s="4" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="5" spans="3:8">
-      <c r="C5" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="D5" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="E5" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="F5" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="G5" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="H5" s="4" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="6" s="1" customFormat="1" spans="3:8">
-      <c r="C6" s="5">
+      <c r="D9" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="D6" s="5">
+      <c r="E9" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="E6" s="5">
-        <v>1</v>
-      </c>
-      <c r="F6" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="G6" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="H6" s="5">
-        <v>30002</v>
-      </c>
-    </row>
-    <row r="7" spans="3:8">
-      <c r="C7" s="5">
-        <v>2</v>
-      </c>
-      <c r="D7" s="5">
-        <v>1</v>
-      </c>
-      <c r="E7" s="5">
-        <v>1</v>
-      </c>
-      <c r="F7" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="G7" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="H7" s="5">
-        <v>30003</v>
-      </c>
-    </row>
-    <row r="8" spans="3:8">
-      <c r="C8" s="5">
-        <v>3</v>
-      </c>
-      <c r="D8" s="5">
-        <v>1</v>
-      </c>
-      <c r="E8" s="5">
-        <v>1</v>
-      </c>
-      <c r="F8" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="G8" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="H8" s="5">
-        <v>30004</v>
-      </c>
-    </row>
-    <row r="9" spans="3:8">
-      <c r="C9" s="5">
-        <v>4</v>
-      </c>
-      <c r="D9" s="5">
-        <v>1</v>
-      </c>
-      <c r="E9" s="5">
-        <v>1</v>
-      </c>
-      <c r="F9" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="G9" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="H9" s="5"/>
-    </row>
-    <row r="10" spans="3:8">
-      <c r="C10" s="5">
-        <v>5</v>
-      </c>
-      <c r="D10" s="5">
-        <v>1</v>
-      </c>
-      <c r="E10" s="5">
-        <v>1</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="G10" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="H10" s="5"/>
-    </row>
-    <row r="11" spans="3:8">
-      <c r="C11" s="5">
-        <v>6</v>
-      </c>
-      <c r="D11" s="5">
-        <v>1</v>
-      </c>
-      <c r="E11" s="5">
-        <v>1</v>
-      </c>
-      <c r="F11" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="G11" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="H11" s="5"/>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>Location</t>
+        </is>
+      </c>
+      <c r="G9" s="3" t="inlineStr">
+        <is>
+          <t>Location</t>
+        </is>
+      </c>
+      <c r="H9" s="5" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.699305555555556" right="0.699305555555556" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
+  <pageSetup orientation="portrait" paperSize="9"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="C3:H10"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.35" outlineLevelCol="7"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="C1:H10"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="12.35"/>
   <cols>
-    <col min="1" max="1" width="21.1238938053097" style="2" customWidth="1"/>
-    <col min="2" max="2" width="12.7522123893805" style="2" customWidth="1"/>
-    <col min="3" max="5" width="12.6283185840708" style="3" customWidth="1"/>
-    <col min="6" max="6" width="15.3716814159292" style="3" customWidth="1"/>
-    <col min="7" max="8" width="13.1238938053097" style="3" customWidth="1"/>
-    <col min="9" max="16384" width="9" style="2"/>
+    <col width="21.1238938053097" customWidth="1" style="2" min="1" max="1"/>
+    <col width="12.7522123893805" customWidth="1" style="2" min="2" max="2"/>
+    <col width="12.6283185840708" customWidth="1" style="3" min="3" max="5"/>
+    <col width="15.3716814159292" customWidth="1" style="3" min="6" max="6"/>
+    <col width="13.1238938053097" customWidth="1" style="3" min="7" max="8"/>
+    <col width="9" customWidth="1" style="2" min="9" max="16384"/>
   </cols>
   <sheetData>
-    <row r="3" spans="3:8">
-      <c r="C3" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="F3" s="4" t="s">
+    <row r="1"/>
+    <row r="2"/>
+    <row r="3">
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>Id</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>所属进程</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>所属区</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>类型</t>
+        </is>
+      </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>名字</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>外网端口</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>Id</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>Process</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>Zone</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>SceneType</t>
+        </is>
+      </c>
+      <c r="G4" s="4" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>Port</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="G5" s="4" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" customFormat="1" s="1">
+      <c r="C6" s="5" t="n">
+        <v>400</v>
+      </c>
+      <c r="D6" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="G3" s="4" t="s">
+      <c r="E6" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="F6" s="5" t="inlineStr">
+        <is>
+          <t>RouterManager</t>
+        </is>
+      </c>
+      <c r="G6" s="5" t="inlineStr">
+        <is>
+          <t>RouterManager</t>
+        </is>
+      </c>
+      <c r="H6" s="5" t="n">
+        <v>30300</v>
+      </c>
+    </row>
+    <row r="7" customFormat="1" s="1">
+      <c r="C7" s="5" t="n">
+        <v>401</v>
+      </c>
+      <c r="D7" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="H3" s="4" t="s">
+      <c r="E7" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="F7" s="5" t="inlineStr">
+        <is>
+          <t>Router</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>Router01</t>
+        </is>
+      </c>
+      <c r="H7" s="5" t="n">
+        <v>30301</v>
+      </c>
+    </row>
+    <row r="8" customFormat="1" s="1">
+      <c r="C8" s="5" t="n">
+        <v>402</v>
+      </c>
+      <c r="D8" s="5" t="n">
         <v>5</v>
       </c>
+      <c r="E8" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="F8" s="5" t="inlineStr">
+        <is>
+          <t>Router</t>
+        </is>
+      </c>
+      <c r="G8" s="5" t="inlineStr">
+        <is>
+          <t>Router02</t>
+        </is>
+      </c>
+      <c r="H8" s="5" t="n">
+        <v>30302</v>
+      </c>
     </row>
-    <row r="4" spans="3:8">
-      <c r="C4" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="D4" s="4" t="s">
+    <row r="9" customFormat="1" s="1">
+      <c r="C9" s="5" t="n">
+        <v>403</v>
+      </c>
+      <c r="D9" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="E4" s="4" t="s">
+      <c r="E9" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="F9" s="5" t="inlineStr">
+        <is>
+          <t>Router</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>Router03</t>
+        </is>
+      </c>
+      <c r="H9" s="5" t="n">
+        <v>30303</v>
+      </c>
+    </row>
+    <row r="10" customFormat="1" s="1">
+      <c r="C10" s="5" t="n">
+        <v>404</v>
+      </c>
+      <c r="D10" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="F4" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="G4" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="H4" s="4" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="5" spans="3:8">
-      <c r="C5" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="D5" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="E5" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="F5" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="G5" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="H5" s="4" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="6" s="1" customFormat="1" spans="3:8">
-      <c r="C6" s="5">
-        <v>400</v>
-      </c>
-      <c r="D6" s="5">
+      <c r="E10" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="E6" s="5">
-        <v>3</v>
-      </c>
-      <c r="F6" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="G6" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="H6" s="5">
-        <v>30300</v>
-      </c>
-    </row>
-    <row r="7" s="1" customFormat="1" spans="3:8">
-      <c r="C7" s="5">
-        <v>401</v>
-      </c>
-      <c r="D7" s="5">
-        <v>4</v>
-      </c>
-      <c r="E7" s="5">
-        <v>3</v>
-      </c>
-      <c r="F7" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="G7" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="H7" s="5">
-        <v>30301</v>
-      </c>
-    </row>
-    <row r="8" s="1" customFormat="1" spans="3:8">
-      <c r="C8" s="5">
-        <v>402</v>
-      </c>
-      <c r="D8" s="5">
-        <v>5</v>
-      </c>
-      <c r="E8" s="5">
-        <v>3</v>
-      </c>
-      <c r="F8" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="G8" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="H8" s="5">
-        <v>30302</v>
-      </c>
-    </row>
-    <row r="9" s="1" customFormat="1" spans="3:8">
-      <c r="C9" s="5">
-        <v>403</v>
-      </c>
-      <c r="D9" s="5">
-        <v>6</v>
-      </c>
-      <c r="E9" s="5">
-        <v>3</v>
-      </c>
-      <c r="F9" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="G9" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="H9" s="5">
-        <v>30303</v>
-      </c>
-    </row>
-    <row r="10" s="1" customFormat="1" spans="3:8">
-      <c r="C10" s="5">
-        <v>404</v>
-      </c>
-      <c r="D10" s="5">
-        <v>7</v>
-      </c>
-      <c r="E10" s="5">
-        <v>3</v>
-      </c>
-      <c r="F10" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="G10" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="H10" s="5">
+      <c r="F10" s="5" t="inlineStr">
+        <is>
+          <t>Router</t>
+        </is>
+      </c>
+      <c r="G10" s="5" t="inlineStr">
+        <is>
+          <t>Router04</t>
+        </is>
+      </c>
+      <c r="H10" s="5" t="n">
         <v>30304</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.699305555555556" right="0.699305555555556" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
+  <pageSetup orientation="portrait" paperSize="9"/>
 </worksheet>
 </file>